--- a/output/驗機單-信邦電子股份有限公司.xlsx
+++ b/output/驗機單-信邦電子股份有限公司.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-60" yWindow="-60" windowWidth="24120" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="工作表3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作表1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作表3" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'工作表1'!$1:$13</definedName>
@@ -1022,7 +1022,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -1040,26 +1040,26 @@
       <nvPicPr>
         <cNvPr id="16" name="圖片 15" descr="mark-"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="59531" y="107156"/>
           <a:ext cx="423984" cy="421641"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1083,26 +1083,26 @@
       <nvPicPr>
         <cNvPr id="17" name="圖片 16" descr="word mark"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="547687" y="95249"/>
           <a:ext cx="1470025" cy="610819"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1126,25 +1126,25 @@
       <nvPicPr>
         <cNvPr id="12" name="圖片 11"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:srcRect l="6842" t="5822" r="5030" b="2511"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="6842" t="5822" r="5030" b="2511"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5301343" y="3397247"/>
           <a:ext cx="2275114" cy="1919061"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1168,24 +1168,24 @@
       <nvPicPr>
         <cNvPr id="13" name="圖片 12"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4238627" y="4612481"/>
           <a:ext cx="1762338" cy="2195514"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1209,24 +1209,24 @@
       <nvPicPr>
         <cNvPr id="14" name="圖片 13"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="6155531" y="3529012"/>
           <a:ext cx="1859470" cy="2555730"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1250,24 +1250,24 @@
       <nvPicPr>
         <cNvPr id="18" name="圖片 17"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="6000750" y="3914775"/>
           <a:ext cx="2333625" cy="2339896"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1590,7 +1590,7 @@
     <row r="1" ht="19.5" customHeight="1" s="105">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>                             </t>
+          <t xml:space="preserve">                             </t>
         </is>
       </c>
       <c r="K1" s="106" t="n"/>
